--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513278_ELIMINGRB12FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513278_ELIMINGRB12FINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6441</v>
+        <v>5.8054</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5764</v>
+        <v>2.9361</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0677</v>
+        <v>2.8694</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6273</v>
+        <v>1.5874</v>
       </c>
       <c r="H2" t="n">
-        <v>1.203</v>
+        <v>1.153</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4243</v>
+        <v>0.4345</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6091</v>
+        <v>0.7648</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9612</v>
+        <v>2.045</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.3522</v>
+        <v>-1.2801</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0182</v>
+        <v>0.8226</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7583</v>
+        <v>-0.892</v>
       </c>
       <c r="O2" t="n">
-        <v>1.7765</v>
+        <v>1.7146</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5622</v>
+        <v>0.548</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2113</v>
+        <v>-0.1356</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6491</v>
+        <v>0.6836</v>
       </c>
       <c r="V2" t="n">
-        <v>3.1789</v>
+        <v>3.2805</v>
       </c>
       <c r="W2" t="n">
-        <v>3.1789</v>
+        <v>3.2805</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0299</v>
+        <v>3.8273</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8501</v>
+        <v>1.7644</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1799</v>
+        <v>2.0629</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2498</v>
+        <v>0.8085</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9805</v>
+        <v>1.0242</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2693</v>
+        <v>-0.2158</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4796</v>
+        <v>0.8622</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3596</v>
+        <v>1.9886</v>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>-1.1264</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2298</v>
+        <v>-0.0537</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3791</v>
+        <v>-0.9644</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1493</v>
+        <v>0.9106</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0003</v>
+        <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5804</v>
+        <v>1.1299</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7114</v>
+        <v>0.2917</v>
       </c>
       <c r="U3" t="n">
-        <v>0.869</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1998</v>
+        <v>0.3311</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6593</v>
+        <v>0.6105</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4596</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.408</v>
+        <v>2.8497</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8199</v>
+        <v>3.4397</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5881</v>
+        <v>-0.59</v>
       </c>
       <c r="G4" t="n">
-        <v>0.836</v>
+        <v>1.1912</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0223</v>
+        <v>0.9498</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1863</v>
+        <v>0.2414</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6889</v>
+        <v>1.5174</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8449</v>
+        <v>1.3958</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.156</v>
+        <v>0.1216</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1471</v>
+        <v>-0.3262</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8226</v>
+        <v>-0.446</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9698</v>
+        <v>0.1198</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6005</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6005</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6314</v>
+        <v>0.4375</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4688</v>
+        <v>0.1744</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1003</v>
+        <v>0.263</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3401</v>
+        <v>1.2211</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5999</v>
+        <v>2.7216</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRÍGUEZ</t>
+          <t>H. APARICIO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5999</v>
+        <v>1.3914</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5999</v>
+        <v>0.9127</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.4788</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5999</v>
+        <v>-0.9023</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5999</v>
+        <v>0.9255</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5999</v>
+        <v>-0.4919</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-1.1648</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5999</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.4104</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.6631</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.2527</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.3431</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.3433</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.7216</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRIGUEZ</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5580000000000001</v>
+        <v>1.2714</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2669</v>
+        <v>1.3428</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2911</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8415</v>
+        <v>3.1106</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7682</v>
+        <v>2.0927</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9267</v>
+        <v>1.0179</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5542</v>
+        <v>2.567</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.196</v>
+        <v>1.9347</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6418</v>
+        <v>0.6323</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2873</v>
+        <v>0.5436</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5722</v>
+        <v>0.158</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2849</v>
+        <v>0.3856</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2001</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2003</v>
+        <v>0.7789</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2001</v>
+        <v>-0.0602</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8379</v>
+        <v>0.1126</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3622</v>
+        <v>-0.1728</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3995</v>
+        <v>-0.6105</v>
       </c>
       <c r="W6" t="n">
-        <v>2.6593</v>
+        <v>0.6105</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2598</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4255</v>
+        <v>1.1848</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5344</v>
+        <v>-0.9697</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9599</v>
+        <v>2.1545</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8229</v>
+        <v>1.7777</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0786</v>
+        <v>1.019</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7443</v>
+        <v>0.7587</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1038</v>
+        <v>0.1526</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1799</v>
+        <v>0.1847</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0762</v>
+        <v>-0.0322</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7191</v>
+        <v>1.6251</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.8343</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8205</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6778</v>
+        <v>0.1608</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6379</v>
+        <v>-0.1486</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0399</v>
+        <v>0.3094</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>H. APARICIO RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3367</v>
+        <v>0.6079</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4508</v>
+        <v>0.6079</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1141</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.073</v>
+        <v>0.6079</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0507</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0223</v>
+        <v>0.6079</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4249</v>
+        <v>0.6079</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8231</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6018</v>
+        <v>0.6079</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6481</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2276</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4205</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2003</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8002</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9361</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5734</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3626</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5999</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1811</v>
+        <v>0.0394</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.374</v>
+        <v>-2.178</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1928</v>
+        <v>2.2174</v>
       </c>
       <c r="G9" t="n">
-        <v>1.189</v>
+        <v>0.6828</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5719</v>
+        <v>1.7698</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7609</v>
+        <v>-1.087</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.429</v>
+        <v>-0.1214</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.549</v>
+        <v>2.6736</v>
       </c>
       <c r="L9" t="n">
-        <v>0.12</v>
+        <v>-2.7951</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6181</v>
+        <v>0.8042</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0229</v>
+        <v>-0.9038</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6409</v>
+        <v>1.708</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.8014</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.0017</v>
+        <v>-2.921</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2003</v>
+        <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9508</v>
+        <v>0.3556</v>
       </c>
       <c r="T9" t="n">
-        <v>3.0568</v>
+        <v>0.3055</v>
       </c>
       <c r="U9" t="n">
-        <v>0.894</v>
+        <v>0.05</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>I. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4543</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.832</v>
+        <v>-1.179</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3777</v>
+        <v>0.3569</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5943000000000001</v>
+        <v>-0.5695</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7915</v>
+        <v>0.3674</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1972</v>
+        <v>-0.9369</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4376</v>
+        <v>-1.288</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5429</v>
+        <v>0.0411</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.9805</v>
+        <v>-1.329</v>
       </c>
       <c r="M10" t="n">
-        <v>1.032</v>
+        <v>0.7185</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7514</v>
+        <v>0.3263</v>
       </c>
       <c r="O10" t="n">
-        <v>1.7834</v>
+        <v>0.3921</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6005</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0009</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4004</v>
+        <v>0.3895</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0322</v>
+        <v>0.3316</v>
       </c>
       <c r="T10" t="n">
-        <v>0.08690000000000001</v>
+        <v>-0.1384</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0547</v>
+        <v>0.47</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5196</v>
+        <v>1.2211</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. MONTERO ISLA</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7153</v>
+        <v>-1.2747</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3677</v>
+        <v>-1.8209</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6523</v>
+        <v>0.5462</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5599</v>
+        <v>-1.4993</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3824</v>
+        <v>-2.1024</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9423</v>
+        <v>0.6031</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.316</v>
+        <v>-1.8981</v>
       </c>
       <c r="K11" t="n">
-        <v>0.04</v>
+        <v>-1.8498</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.356</v>
+        <v>-0.0483</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7561</v>
+        <v>0.3988</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3425</v>
+        <v>-0.2526</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4137</v>
+        <v>0.6514</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6002</v>
+        <v>0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4001</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4448</v>
+        <v>0.9714</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2511</v>
+        <v>0.4919</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6959</v>
+        <v>0.4794</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.9416</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1998</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1998</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.88</v>
+        <v>-2.1839</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8287</v>
+        <v>-5.0391</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9487</v>
+        <v>2.8552</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4889</v>
+        <v>1.1856</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0663</v>
+        <v>-0.5177</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5774</v>
+        <v>1.7033</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0083</v>
+        <v>-0.2528</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.894</v>
+        <v>-0.3744</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1143</v>
+        <v>0.1216</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5194</v>
+        <v>1.4384</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1723</v>
+        <v>-0.1433</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6917</v>
+        <v>1.5817</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2001</v>
+        <v>-4.6737</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-5.8421</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3488</v>
+        <v>1.8631</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6603</v>
+        <v>1.0558</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6885</v>
+        <v>0.8073</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4596</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.7714</v>
+        <v>12.6966</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3728</v>
+        <v>-0.1830999999999996</v>
       </c>
       <c r="F13" t="n">
-        <v>15.1441</v>
+        <v>12.8799</v>
       </c>
       <c r="G13" t="n">
-        <v>8.101900000000001</v>
+        <v>7.980600000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1026</v>
+        <v>3.927900000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9993</v>
+        <v>4.0526</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1611</v>
+        <v>2.4197</v>
       </c>
       <c r="K13" t="n">
-        <v>6.112599999999999</v>
+        <v>6.874500000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.951700000000001</v>
+        <v>-4.454800000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>6.941</v>
+        <v>5.5609</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.01</v>
+        <v>-2.9466</v>
       </c>
       <c r="O13" t="n">
-        <v>8.9512</v>
+        <v>8.507299999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.0017</v>
+        <v>-5.8421</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.005</v>
+        <v>-16.5527</v>
       </c>
       <c r="R13" t="n">
-        <v>11.003</v>
+        <v>10.7105</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6122</v>
+        <v>5.3946</v>
       </c>
       <c r="T13" t="n">
-        <v>0.535</v>
+        <v>1.666</v>
       </c>
       <c r="U13" t="n">
-        <v>4.077400000000001</v>
+        <v>3.7283</v>
       </c>
       <c r="V13" t="n">
-        <v>5.0588</v>
+        <v>5.1637</v>
       </c>
       <c r="W13" t="n">
-        <v>11.9363</v>
+        <v>12.2838</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.877599999999999</v>
+        <v>-7.1202</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.544</v>
+        <v>4.1124</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2923</v>
+        <v>2.9353</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2517</v>
+        <v>1.1771</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0743</v>
+        <v>4.0217</v>
       </c>
       <c r="H14" t="n">
-        <v>1.456</v>
+        <v>1.4316</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6183</v>
+        <v>2.5901</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5411</v>
+        <v>3.6413</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2993</v>
+        <v>2.3605</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2417</v>
+        <v>1.2808</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5332</v>
+        <v>0.3804</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8434</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3766</v>
+        <v>1.3093</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5295</v>
+        <v>0.1754</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7516</v>
+        <v>0.2677</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.222</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0514</v>
+        <v>2.0573</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9355</v>
+        <v>1.473</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1159</v>
+        <v>0.5843</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.6256</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0238</v>
+        <v>-0.9122</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3318</v>
+        <v>0.2866</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.4687</v>
+        <v>-1.3191</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.5087</v>
+        <v>-1.3597</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.6935</v>
       </c>
       <c r="N15" t="n">
-        <v>0.485</v>
+        <v>0.4474</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2918</v>
+        <v>0.2461</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5633</v>
+        <v>1.5076</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1653</v>
+        <v>0.4532</v>
       </c>
       <c r="U15" t="n">
-        <v>1.398</v>
+        <v>1.0544</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4204</v>
+        <v>-0.3826</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2389</v>
+        <v>2.339</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.6593</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0938</v>
+        <v>1.3928</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2932</v>
+        <v>0.5178</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8006</v>
+        <v>0.875</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1005</v>
+        <v>1.0698</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0887</v>
+        <v>-0.1037</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1892</v>
+        <v>1.1735</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6895</v>
       </c>
       <c r="K16" t="n">
-        <v>0.04</v>
+        <v>0.0411</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6399</v>
+        <v>0.6484</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4206</v>
+        <v>0.3803</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1287</v>
+        <v>-0.1447</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2067</v>
+        <v>0.1283</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1867</v>
+        <v>0.0231</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0201</v>
+        <v>0.1052</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7533</v>
+        <v>1.1427</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0725</v>
+        <v>0.4838</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6808</v>
+        <v>0.6589</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3912</v>
+        <v>2.3945</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9016</v>
+        <v>0.9571</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4897</v>
+        <v>1.4375</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8648</v>
+        <v>3.0181</v>
       </c>
       <c r="K17" t="n">
-        <v>1.545</v>
+        <v>1.6807</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3198</v>
+        <v>1.3374</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4735</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6434</v>
+        <v>-0.7236</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1699</v>
+        <v>0.1001</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3423</v>
+        <v>0.7023</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0091</v>
+        <v>0.1394</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3332</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. VIÑO LOPEZ</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5998</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5998</v>
+        <v>-1.4446</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2.1276</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5998</v>
+        <v>-0.1717</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5998</v>
+        <v>1.3892</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-1.5608</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5998</v>
+        <v>0.2637</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5998</v>
+        <v>2.3299</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-2.0662</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.4353</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.9407</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.5054</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.5316</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.7033</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.7346</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.0314</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>N. VIÑO LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4125</v>
+        <v>0.6158</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8086</v>
+        <v>0.6158</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3962</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2702</v>
+        <v>0.6158</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3102</v>
+        <v>0.6158</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5803</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0036</v>
+        <v>0.6158</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1466</v>
+        <v>0.6158</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.1502</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8365</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5698</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6005</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6007</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7427</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.8048</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6691</v>
+        <v>-0.039</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4112</v>
+        <v>-0.6112</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7421</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.3999</v>
+        <v>-3.4235</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8772</v>
+        <v>-0.9258</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5227</v>
+        <v>-2.4977</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.1701</v>
+        <v>-3.0973</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4981</v>
+        <v>-0.4798</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.672</v>
+        <v>-2.6175</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2298</v>
+        <v>-0.3262</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3791</v>
+        <v>-0.446</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9294</v>
+        <v>-0.2582</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1602</v>
+        <v>-0.515</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2308</v>
+        <v>0.2568</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="W20" t="n">
-        <v>2.9191</v>
+        <v>3.0011</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2636</v>
+        <v>-1.1959</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2381</v>
+        <v>-1.2005</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0255</v>
+        <v>0.0046</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4443</v>
+        <v>-0.4571</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0443</v>
+        <v>-0.0518</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3999</v>
+        <v>-0.4053</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4643</v>
+        <v>-0.4776</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0643</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3999</v>
+        <v>-0.4053</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2192</v>
+        <v>-0.1546</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2578</v>
+        <v>-0.2473</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0387</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6756</v>
+        <v>-1.3441</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9418</v>
+        <v>-2.6833</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2662</v>
+        <v>1.3391</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6047</v>
+        <v>-1.5922</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0604</v>
+        <v>1.0319</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6651</v>
+        <v>-2.6241</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7105</v>
+        <v>-1.5988</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6395</v>
+        <v>1.6832</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.35</v>
+        <v>-3.282</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1058</v>
+        <v>0.0067</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.6513</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6849</v>
+        <v>0.6579</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6714</v>
+        <v>-1.3099</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0313</v>
+        <v>-0.8897</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.64</v>
+        <v>-0.4202</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7133</v>
+        <v>-3.7923</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8127</v>
+        <v>-2.6821</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-1.1102</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2055</v>
+        <v>-1.1319</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6815</v>
+        <v>-2.5825</v>
       </c>
       <c r="I23" t="n">
-        <v>1.476</v>
+        <v>1.4506</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2032</v>
+        <v>-0.969</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.845</v>
+        <v>-1.6418</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6418</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0023</v>
+        <v>-0.163</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8365</v>
+        <v>-0.9407</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7685</v>
+        <v>-0.8609</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.0367</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.7396</v>
+        <v>-2.7732</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. MARCIEL</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5075</v>
+        <v>-4.2741</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8231</v>
+        <v>-3.9704</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6844</v>
+        <v>-0.3037</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5</v>
+        <v>-2.6098</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.5692</v>
+        <v>-1.3958</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0692</v>
+        <v>-1.214</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.592</v>
+        <v>-2.4521</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.712</v>
+        <v>-0.4669</v>
       </c>
       <c r="L24" t="n">
-        <v>0.12</v>
+        <v>-1.9852</v>
       </c>
       <c r="M24" t="n">
-        <v>0.092</v>
+        <v>-0.1577</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8572</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9492</v>
+        <v>0.7712</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2001</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2001</v>
+        <v>-1.1684</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4001</v>
+        <v>1.1684</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7479</v>
+        <v>-0.7743</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.031</v>
+        <v>-0.6294</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7169</v>
+        <v>-0.1449</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4596</v>
+        <v>-0.89</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4596</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. VAL GUTIERREZ</t>
+          <t>E. MARCIEL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0974</v>
+        <v>-4.3984</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4926</v>
+        <v>-3.1456</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6048</v>
+        <v>-1.2528</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.5625</v>
+        <v>-2.5114</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2138</v>
+        <v>-3.5633</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.7762</v>
+        <v>1.0519</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.9122</v>
+        <v>-2.5364</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7998</v>
+        <v>-2.658</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.712</v>
+        <v>0.1216</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6502</v>
+        <v>0.0251</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.586</v>
+        <v>-0.9052</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0642</v>
+        <v>0.9303</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0003</v>
+        <v>-0.1947</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4004</v>
+        <v>0.3895</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7353</v>
+        <v>-0.5812</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.4144</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1552</v>
+        <v>-0.1668</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.1998</v>
+        <v>-1.5005</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.1998</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>D. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.4748</v>
+        <v>-4.7356</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.8094</v>
+        <v>-3.1678</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6654</v>
+        <v>-1.5678</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.5888</v>
+        <v>-3.5593</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.3596</v>
+        <v>0.1816</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.2292</v>
+        <v>-3.7409</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.5864</v>
+        <v>-1.837</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5162</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.0702</v>
+        <v>-2.658</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0023</v>
+        <v>-1.7223</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.8434</v>
+        <v>-0.6394</v>
       </c>
       <c r="O26" t="n">
-        <v>0.841</v>
+        <v>-1.0829</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.2003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2003</v>
+        <v>1.3632</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0264</v>
+        <v>-0.3447</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.2824</v>
+        <v>-0.3572</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7439</v>
+        <v>0.0125</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.8597</v>
+        <v>-1.2211</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.1195</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-11.7715</v>
+        <v>-9.775399999999998</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.1442</v>
+        <v>-12.8798</v>
       </c>
       <c r="F27" t="n">
-        <v>3.3727</v>
+        <v>3.104200000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>-8.1021</v>
+        <v>-7.980700000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.1025</v>
+        <v>-3.9279</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.999200000000001</v>
+        <v>-4.0526</v>
       </c>
       <c r="J27" t="n">
-        <v>-6.9411</v>
+        <v>-5.5608</v>
       </c>
       <c r="K27" t="n">
-        <v>2.01</v>
+        <v>2.9466</v>
       </c>
       <c r="L27" t="n">
-        <v>-8.9512</v>
+        <v>-8.507299999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.1607</v>
+        <v>-2.4196</v>
       </c>
       <c r="N27" t="n">
-        <v>-6.1126</v>
+        <v>-6.8744</v>
       </c>
       <c r="O27" t="n">
-        <v>4.951899999999999</v>
+        <v>4.454599999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>6.0019</v>
+        <v>5.8421</v>
       </c>
       <c r="Q27" t="n">
-        <v>-11.0032</v>
+        <v>-10.7104</v>
       </c>
       <c r="R27" t="n">
-        <v>17.0047</v>
+        <v>16.5527</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.612400000000001</v>
+        <v>-2.4735</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.077199999999999</v>
+        <v>-3.7283</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5350000000000003</v>
+        <v>1.2552</v>
       </c>
       <c r="V27" t="n">
-        <v>-5.0589</v>
+        <v>-5.1638</v>
       </c>
       <c r="W27" t="n">
-        <v>6.8774</v>
+        <v>7.1202</v>
       </c>
       <c r="X27" t="n">
-        <v>-11.9364</v>
+        <v>-12.2837</v>
       </c>
     </row>
   </sheetData>
